--- a/bd1.xlsx
+++ b/bd1.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,10 +4024,8 @@
           <t>KOUASSI Louis Gerard</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0102989154</t>
-        </is>
+      <c r="E70" t="n">
+        <v>102989154</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4130,10 +4128,8 @@
           <t>KONAN  Atse Franck Désiré</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0787347707</t>
-        </is>
+      <c r="E72" t="n">
+        <v>787347707</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4183,10 +4179,8 @@
           <t>MOBIO Adja Axel Prince Yvon</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>0141583425</t>
-        </is>
+      <c r="E73" t="n">
+        <v>141583425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4236,10 +4230,8 @@
           <t>KONE Alligué Samirah Angela Mauricette</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0758422493</t>
-        </is>
+      <c r="E74" t="n">
+        <v>758422493</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4269,6 +4261,1330 @@
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>44944</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>DOUCOURE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Oumou</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DOUCOURE Oumou</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Analyse de la gestion du risque inhérent à l'octroi de crédit bancaire aux entreprises: cas de la Banque Populaire de Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Banque populaire</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>N'GUESSA Simon Pierre</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>44945</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NIAMKE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ahdjey David Loic Emmanuel</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NIAMKE Ahdjey David Loic Emmanuel</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Effet de l'ouverture commercial et des flux de capitaux sur la croissance économique en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Economie de développement</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Economie de développement</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Economie de développement</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>AKA Brou Emmanuel</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>44945</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BENIAMBIE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Aka Ephraim Herman</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BENIAMBIE Aka Ephraim Herman</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mise en place d'un manuel de procédure de gestion de trésorie</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>N'GUESSA Simon Pierre</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>44946</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TRAORE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BINTA</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TRAORE BINTA</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>L'évaluation du contrôle interne d'une entreprise de distribution d'un service financier numérique</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>FOFANA Andom</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>44844</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BAOUNA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Domo</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BAOUNA Domo</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Analyse des effets du commerce international sur la sécurité alimentaire des ménages: cas des ménages du Tchad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>KONE Salif</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>44952</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>OUATTARA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Kra</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OUATTARA Kra</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Impact des dépenses publiques sociales sur la croissance économique en CI</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>KOUAKOU Auguste</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>44620</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>OUATTARA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Abdel Kader</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OUATTARA Abdel Kader</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Contribution à l'amélioration de l'élaboration des états financiers des entités dans le cadre de la mission de visa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>FOFANA Adom</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>44957</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TANOE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ahoba Marie-Déirée</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TANOE Ahoba Marie-Déirée</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>767469615</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Contribution de la revision comptable à la gestion financières et comptable d'une entreprise; cas de COMTRATS</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>COMTRATS</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>FOFANA Andom</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>45013</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BLE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Israel Djedje</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BLE Israel Djedje</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>La fiscalité comme lévier de développement: cas de la Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>MOUSSA Kouame Richard</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>45013</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ATTA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>N'Doua Jean Christian</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ATTA N'Doua Jean Christian</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Analyse des facteurs limitant la production des éléveurs de porcs de la ville d'Abidjan et ses alentours</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>MOUSSA Kouame Richard</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LAGO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Logblo Olga-Dominique</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LAGO Logblo Olga-Dominique</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Analyse de stratégie de fidélisation des clients de la banque des dépôts du trésor public de Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Banque du trésor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>SANGARE Tchetien</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>45103</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KOUKONI</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Gloria Marina</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>KOUKONI Gloria Marina</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Conquête et fidélisation de la clientèle, un jeu pour les banques aujour'hui: Cas de la BHCI</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>BHCI</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>APKESSE</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TRAORE</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Cadic Laeticia Ley</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>TRAORE Cadic Laeticia Ley</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Finances islamique et inclusion financière</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>MOUSSA Kouamé Richard</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AVY</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sombo Marie-Andrée Eugenie</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AVY Sombo Marie-Andrée Eugenie</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Fracture numérique et transition démographique en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>KOUAKOU Auguste</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TIAPANI</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Akpa Jean Cyriaque</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>TIAPANI Akpa Jean Cyriaque</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Impact de la COVID-19 sur le commerce électronique en Afrique cas de Jumia</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>KOUAKOU Auguste</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>BAMBA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Awa</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BAMBA Awa</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>La mission du commissaire aux comptes dans la certification du cycle vente-client: cas de la société X</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>SANGARE</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OSSEY</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Reine Marina Aude</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>OSSEY Reine Marina Aude</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Contribution de la mise en oeuvre des recommandations d'audit interne à l'amélioration du processus de gestion des stocks au BNETD</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>BNETD</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>FOFANA Adom</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KOTTY</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Kotty Paul Marie</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>KOTTY Kotty Paul Marie</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Analyse du marché de la téléphonie mobile en Côte d'Ivoire:dynamique du marché et performance des opérateurs</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Sangare Tchetien</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ABIE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Jeanne</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ABIE Jeanne</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Analyse de la mission d'audit des dépenses d'alimentation dans l'administrationn publique: cas du centre régionale des oeuvres Universitaires</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>CROU</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Sangare Tchetien</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>COULIBALY</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Myriam</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>COULIBALY Myriam</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Analyse des risques liés à la gestion du cycle achats fournisseurs dans le cadre d'une mission de CAC: Cas de l'agence TS Immobilier</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>TS Immobilier</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Fofana César</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KOBRON</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ehien</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>KOBRON Ehien</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Evolution de la satisfaction clientèle particuluier à l'offre bancaire de prêt immobilier: Cas de la BHCI</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>BHCI</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>KOUASSI Rufin Cyriaque</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>DAGRI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fleure</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DAGRI Fleure</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Audit du dispositif HSE: cas du BNETD</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>BNETD</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>FOFANA Andom</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ACHO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bah Marie Otnielle</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ACHO Bah Marie Otnielle</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Impact du contrôle interne sur la performance financière de l'entreprise: Cas du BNETD</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>BNETD</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>FOFANA Andom</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>APKA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Agnimel Claude Virgile</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>APKA Agnimel Claude Virgile</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Evaluation du contrôle interne du Cycle Achat: Cas de VOLCAGRO-CI</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>VOLCAGRO-CI</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>FOFANA Andom</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>DOGBO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bisso Gilles Kevine</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>DOGBO Bisso Gilles Kevine</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>L'impact du crédit-bail sur la performance financière: Cas de la BICICI</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>BICICI</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>KOUASSI Rufin Cyriaque</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>45110</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>JOANNY</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tape Waissa Mamita</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>JOANNY Tape Waissa Mamita</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Evaluation des procédures du contrôle interne du cycle Achat/Fournisseur dans le cadre d'une mission de CAC: Cas de la SIA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>FOFANA Andom</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bd1.xlsx
+++ b/bd1.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5586,6 +5586,1336 @@
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>45111</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DOMANDE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Satyogo</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DOMANDE Satyogo</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Evaluation du contrôle interne cycle vente client lors d'une mission d'audit externe: cas de la société alpha</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>BNETD</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>BADINI</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45112</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DON</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Boimin Held</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>DON Boimin Held</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>La mise en place du dispositif de contrôle interne au sein d'une société de production de boissons alcoolisées: Cas du département - productions MIBEM-MIB</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>MIBEM-MIB</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>BADINI</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>45113</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GLOPKOR</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ahoefa Dédé Géorgette</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>GLOPKOR Ahoefa Dédé Géorgette</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>L'effet de la fracture numérique sur la sécurité alimentaire en afrique subsaharienne</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Kouakou Auguste</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>45116</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>KIPRE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Prince Donald</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>KIPRE Prince Donald</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Transition énergétique en Côte d'Ivoire: L'énergie éolienne, une alternative dans le mix-énergétique</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>ASSOUMOU Ella</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>DADIE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Dogo Jérôme</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DADIE Dogo Jérôme</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Effet de la corruption sur la croissance économique dans les pays en développement: cas de L'UEMOA</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>ASSOUMOU Ella</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KOFFI</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Adamoh Yves Christian</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>KOFFI Adamoh Yves Christian</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Optimisation des délais de traitement de sinistre pour les produits de prévoyance cas WAFA Assurance vie</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>WAFA Assurance</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>NOE Coulibay</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>45240</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ABBY</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Gah Malika</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>ABBY Gah Malika</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Analyse des déterminants de l'acceptabilité des procédures de développement administratifs en ligne par les ivoiriens d'abidjan et ses alentours</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>KOUAKOU Auguste</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>45296</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>GOLOT</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Gah Octavie</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>GOLOT Gah Octavie</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Analyse des coûts d'exploitation des véhicules: cas de l'unité agricole intégré d'EHANIA</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>EHANIA</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>FOFANA Adom</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SIMDAYIKE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Cyriaque</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SIMDAYIKE Cyriaque</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Les mécanismes de mise en place optimale d'un cycle de vie du crédit dans une SFD en Côte d'Ivoire: Cas de DIFIM SA</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>DIFIM SA</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>KOUASSI Rufin</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>AFFIAN</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Astride Lynda Ama</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AFFIAN Astride Lynda Ama</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Diagnostic qualité des missions d'assistance comptable au sein du Cabinet 3C</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>3C</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>LOUA</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Dervine Anne Elisabeth Gausseu</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LOUA Dervine Anne Elisabeth Gausseu</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>L'accessibilité des PME aux financement du marché par les banques: cas de la banque populaire de Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>banque populaire</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>FANNY</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Inza Ladji Habib</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>FANNY Inza Ladji Habib</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Effet de la gouvernance sur la croissance économique en Afrique</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>MOUSSA Kouamé Richard</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SORO</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Kinignari Zakaria</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SORO Kinignari Zakaria</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Analyse des déterminants des stratégies d'adaptations des riziculteurs face au changements climatique: un exemple de la région du Kabadougou</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Salif Koné</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CAMINO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tanobla Morisson</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CAMINO Tanobla Morisson</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>L'influence de la GRC sur la performance financière de la banque: cas de la SIB</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>SANGARE</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>EKOU</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Tanoh Yves Elfried</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EKOU Tanoh Yves Elfried</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Impact du commerce international sur la croissance économique: Rôle de la corruption en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>KONE Salif</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SACOH</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Dorcas</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SACOH Dorcas</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Effets des chocs conjoncturelles sur la banlance commerciale des pays de la CEDEAO</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>ASSOUMOU Ella</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>COULIBALY</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Siombin Nangoti Ali</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>COULIBALY Siombin Nangoti Ali</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Contribution de la cellule de remediaton a la mise à jour des données clientèles: Cas de la Bridge Bank Group Ci</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Bridge Bank</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>SANGARE Tchetchien</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Agui</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Emmanuella</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Agui Emmanuella</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Amélioration de la satisfaction client dans les établissements bancaires: cas de la BHCI Treichville</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>BHCI</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Sangare Tchetien</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ABIE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Jeanne</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ABIE Jeanne</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Analyse de la mission d'audit des dépenses d'alimentation dans l'administrationn publique: cas du centre régionale des oeuvres Universitaires</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>CROU</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Sangare Tchetien</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>KOUADIO</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Aguely Jean</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>KOUADIO Aguely Jean</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Evaluation des risques dans une société de Gestion Immoilière: Une approche d'audit pour la prévention et la détection des risques de fraudes dans la société Beta</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Fofana César</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TRAORE</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Chintchon Aminata</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TRAORE Chintchon Aminata</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Contribution du contrôle interne à l'amélioration de la gestion des risques opérationnelles: cas de l'entreprise alpha</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>SANGARE Tchétien</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45387</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ADJEHI</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>N'Tah Carine</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ADJEHI N'Tah Carine</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Contribution de l'audit légal à la performance organisationnelle et financière des entreprises: Cas de la société HAMA</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>HAMA</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>FOFANA Adom</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45394</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>AHOUTY</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tekia</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AHOUTY Tekia</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Impact des investissements directs étrangers sur l'environnement en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>KOUADIO Benié</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45469</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ZANKOU</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Nathalie</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ZANKOU Nathalie</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Contribution de la gestion des risques organisationnels à la bonne gouvernance des institutions: Cas de CARITAS CI</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>CARITAS CI</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>SANGARE Tchetien</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45481</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>KOMENAN</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Jean Marie Vianey</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>KOMENAN Jean Marie Vianey</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>La commercialisation des produits dans une micro-assurance: cas de l'UNACOOPEC-CI</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>DOMOA Danielle</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>DIOKE Djedjoro</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Djedjoro Antoinnette</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>DIOKE Djedjoro Antoinnette</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>0779968672</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Impact de la digitalisation des produits et services bancaires sur la relation client: Cas de BOA-CI</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>BOA-CI</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bd1.xlsx
+++ b/bd1.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M126"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6916,6 +6916,283 @@
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45392</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>KOUADIO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Kouassi Samuel</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>KOUADIO Kouassi Samuel</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Audit des opérations de change à l'international et geston du risque de change: cas d'ECOBANK</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>ECOBANK</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>YAO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Amoin Ble Myrlène Shiva</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>YAO Amoin Ble Myrlène Shiva</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0777826517</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Effet de l'implémentation du logiciel ODOO sur les résultats comptables de MOYE SARL: Une étude exploratoire</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>MOYE SARL</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Simon</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GAYE</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Mariama</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>GAYE Mariama</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0707381952</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Analyse du processus d'octroi de crédits aux PME: cas de la banque populaire</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Banque populaire</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Simon</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>COMPAORE</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Boris Cedric</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>COMPAORE Doris Cedric</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0777282902</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Analyse de la relation entre les caractéristiques des particuliers et les impayés</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45385</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ELEMEHA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Danielle-Esther</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>ELEMEHA Danielle-Esther</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0749836044</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Conquête et fidélisation de la clientèle retraitée d'une microfinance: cas du fonds international pour le développement de la retraite active FIDRA</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>FIDRA</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>DOMOA Daniel</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bd1.xlsx
+++ b/bd1.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>GRATIER ANTOINNE</t>
+          <t>N'GRATIER ANTOINNE</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>GRATIER ANTOINNE</t>
+          <t>N'GRATIER ANTOINNE</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>GRATIER ANTOINNE</t>
+          <t>N'GRATIER ANTOINNE</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>GRATIER ANTOINNE</t>
+          <t>N'GRATIER ANTOINNE</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>GRATIER ANTOINNE</t>
+          <t>N'GRATIER ANTOINNE</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>GRATIER ANTOINNE</t>
+          <t>N'GRATIER ANTOINNE</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>GRATIER ANTOINNE</t>
+          <t>N'GRATIER ANTOINNE</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6842,12 +6842,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -6910,15 +6910,17 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>N'DRI Yachine</t>
+          <t>SANGARE Tchétien</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>45392</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -6938,7 +6940,7 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Audit des opérations de change à l'international et geston du risque de change: cas d'ECOBANK</t>
+          <t>Audit des opérations de change à l'international et gestion du risque de change : cas d'Ecobank-CI</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -6948,12 +6950,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6970,8 +6972,10 @@
       <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>45483</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -6980,27 +6984,27 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Amoin Ble Myrlène Shiva</t>
+          <t>Amoin Ble Myrlene Shiva</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>YAO Amoin Ble Myrlène Shiva</t>
+          <t>YAO Amoin Ble Myrlene Shiva</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>0777826517</t>
+          <t>07-77-82-65-17</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Effet de l'implémentation du logiciel ODOO sur les résultats comptables de MOYE SARL: Une étude exploratoire</t>
+          <t>Effet de l'implémentation du logiciel ODOO sur les résultats comptables de MOYE SARL : une étude exploratoire</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Audit et contrôle</t>
+          <t>Audit et controle</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7015,20 +7019,22 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>MOYE SARL</t>
+          <t>MOYE-SARL</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>N'GUESSAN Simon</t>
+          <t>N'GUESSAN Kouadio Simon</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>45483</v>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -7042,17 +7048,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>GAYE Mariama</t>
+          <t>GAYE Mariam</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>0707381952</t>
+          <t>07-07-38-19-52</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Analyse du processus d'octroi de crédits aux PME: cas de la banque populaire</t>
+          <t>Analyse du processus d'octroi de crédit aux PME : cas de la banque populaire de la Côte d'Ivoire</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7062,30 +7068,32 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Banque populaire</t>
+          <t>Banque Populaire</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>N'GUESSAN Simon</t>
+          <t>N'GUESSAN Kouadio Simon</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>45483</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -7094,17 +7102,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boris Cedric</t>
+          <t>Doris Paul Cedric</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>COMPAORE Doris Cedric</t>
+          <t>COMPAORE Doris Paul Cedric</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>0777282902</t>
+          <t>07-77-28-20-02</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7119,12 +7127,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -7137,8 +7145,10 @@
       <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>45385</v>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -7157,12 +7167,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>0749836044</t>
+          <t>07-49-83-60-44</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Conquête et fidélisation de la clientèle retraitée d'une microfinance: cas du fonds international pour le développement de la retraite active FIDRA</t>
+          <t>Conquête et fidélisation de la clientèle retraitée d'une microfinance : cas du FIDRA</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7172,12 +7182,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Banque et assurane</t>
+          <t>Banque et assurance</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7187,11 +7197,3081 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>DOMOA Daniel</t>
+          <t>DOMOA Danielle</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>HAMANI</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Zenabou Marie-Ange</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>HAMANI Zenabou Marie-Ange</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>07-79-28-14-99</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Analyse de l'évolution de la performance financière des PME à partir des états financiers</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Kouadio Simon</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GBESSE</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Amoin Marie</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>GBESSE Amoin Marie</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>07-58-02-63-16</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Analyse du système de recouvrement de l'ING-BTP</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>ING-BTP</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BENOU</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Kouamé Georges Sandrine</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BENOU Kouamé Georges Sandrine</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>07-88-32-99-59</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Enjeux et perspectives de l'assistance funeraille en Côte d'Ivoire : cas de NSIA assurance</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>NSIA assurance</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>BADINI Haoua</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DJE</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Eunix Madyran Grace Erica</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DJE Eunix Madyran Grace Erica</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>07-49-36-90-38</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Amélioration des critères d'octroi de crédit aux PME : cas de la Banque populaire de Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Banque Populaire</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>BADINI Haoua</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BROU</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Amoua Nadia</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BROU Amoua Nadia</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>07-57-79-51-85</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Gestion du risque dans l'octroi de crédit aux PME : cas de la BHCI</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>BHCI</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>BADINI Haoua</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-10  00:00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ANATU</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Senankpon Mindeton Isaac</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ANATU Senankpon Mindeton Isaac</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>01-42-26-91-72</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Analyse des stratégies de fidélisation de la clientèle PME dans les assurances : Cas de SUMU assurance vie</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>SUNU assurance vie</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>FOFANA Cesar</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-11  00:00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>KOUESSE</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Kemintinhy Onintho Ange Daniel</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>KOUESSE Kemintinhy Onintho Ange Daniel</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>07-89-53-84-99</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse des sorties de contrat à la demande du client: cas de SUNU assurance vie </t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>SUNU assurance vie</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>AMINATA Doumbia</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-11  00:00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>KONAN</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>A. Yann-Loïc</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>KONAN A Yann Loïc</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>07-57-41-62-82</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>L'apport du digital dans le developpement du portefeuille client des compagnies de courtage</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>banque et assurance</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-11  00:00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BALLONO</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>BALLONO Rita</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>07-89-88-69-74</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Effet des impayés de prime sur les délais d'indemnisations</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>N'GRATTIER Antoinne</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-13  00:00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DACOURY</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Zoni Ange</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>DACOURY Zoni Ange</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>07-49-35-44-94</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Analyse exploratoire de la cartographie des risques : cas de la procédure de confidentialité des données du personnel aéronautique de la DeMPA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>DOMA Chayé</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-16  00:00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ASUE</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ASUE Michael</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>01-03-84-42-63</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>La contribution de l'audit interne à la performance des entreprises privées : cas de MEDLOG-CI transport et logistic</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>MEDLOG-CI</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>AHOGNISSO Affi</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-17  00:00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NOUMIN</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>N'Touama Yomo</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NOUMIN N'Touama Yomo</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>L'audit de la passation de marchés publics : cas d'une sociéte d'Etat en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>OUATTARA Bassife</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2024-07-17  00:00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>DIARRASSOUBA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Zeïnab</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DIARRASSOUBA Zeïnab</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Effets de la croissance économique sur les émissions de CO2 en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Economie de développement</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Economie de développement</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Economie de développement</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>AKA Brou Emmanuel</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>45490</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>FOFANA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mariama Sara</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>FOFANA Mariama Sara</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0777788396</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>De l'optimisation du contrôle interne à la performance des ressources humaine d'un cabinet comptable</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>HAMA</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>BADINI</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>45490</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SEH</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Patrice</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SEH Patrice</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0708673539</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Contribution du contrôle à la fiabilité à la conformité de l'information financière dans les entités à but non lucratif</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>AHOGNISSO Angeline</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>45490</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ILBOUDO</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ILBOUDO Benjamin</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0141871588</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Adoption et mise en oeuvre du système comptable des entités à but lucratif: cas de l'association Alpha</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>OUATTARA Bassife</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>45490</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>DOULOU</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Axelle Nelly</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>DOULOU Axelle Nelly</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0788322957</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Gestion du risque et du sinistre en assurance emprunteur: Cas de SAAR Assurance CI</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Banque et assurane</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>SAAR Assurance</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Simon</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>45492</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>OUATTARA Djedjoro</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Somon Abiba</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OUATTARA Somon Abiba</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0779135993</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>L'effet de l'éducation des femmes sur la croissance économique de 1990 à 2022: Méthode ARDL</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>AKA Brou</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>45492</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>MEYER</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Sopie Laeticia</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>MEYER Sopie Laeticia</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0779135993</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Analyse des déterminants de l'accès au financement des producteurs de noix de cajou dans la region du gontougo en Côte d'Ivoir</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>ZOUNGRANA Placide</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>45498</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>KARAMOKO</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Kobaya Youssef</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>KARAMOKO Kobaya Youssef</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Effet de la performance portuaire et du trafic global de marchandise sur la croissance économique de la Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>KOUADIO Benie</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>45650</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>GUEI</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Lyne Carmen</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>GUEI Lyne Carmen</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0788116260</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Evaluation du dispositif de contrôle interne mis en place pour la gestion des heures supplémentaires: Cas de la CIE</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>CIE</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>AHOGNISSO Angeline</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>45632</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>DIOMANDE</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Abiba</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DIOMANDE Abiba</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0777282902</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Contribution de l'audit légal à l'amélioration du contrôle interne du cycle achats fournisseur d'une entreprise de grande distribution: Cas de ALPHA Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Simon Pierre</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>45632</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>OKOU</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Zarou Axcel Junior</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>OKOU Zarou Axcel Junior</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0778898968</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Contribution de l'audit interne à l'efficacité de la gestion des espaces banalisés sous douane du port autonome d'abidjan</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Port Autonome d'Abidjan</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>FOFANA Andon</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>45632</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>KOFFI</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Kra Claude Noel</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>KOFFI Kra Claude Noel</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0778366656</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Evaluation du cycle achat-fournisseurs dans une entreprise de distribution de produit petrolier</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>FOFANA Adom</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>45632</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HOUSSOU</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Dieu-Donné Adebayo</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>HOUSSOU Dieu-Donné Adebayo</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0153171481</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Analyse de la fiabilité d'une mission de commissariat aux comptes par l'optimisation des procédures d'évaluation des risques d'audit: cas de l'entreprise Alpha</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>BADINI Haoua</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>45632</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>KONATE</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Pelaya Yassina</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>KONATE Pelaya Yassina</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0778505098</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Gestion du risque opérationnel dans l'activité bancaire: cas de la banque du Tresor</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Banque du Trésor</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>45635</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>MANZAN</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ablan Marie-Ines Pamela</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>MANZAN Ablan Marie-Ines Pamela</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0787997563</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Mise en place d'un système d'évaluation de la conformité des entreprises aux normes de LBC/FS par un cabinet comptable cas de FS et associé</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>FS et associé</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>AHOGNISSO Angeline</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>45635</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>BITTY</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ahou Josephine Claire Esson</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>BITTY Ahou Josephine Claire Esson</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0767877710</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Gestion des risques de crédit dans les banques: Cas de la BOA-CI</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>BOA-CI</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>KOUAME</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Hapi Marie Josiane Emma</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>KOUAME Hapi Marie Josiane Emma</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0767877710</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Analyse du return on equity d'un établissement de crédit cas de la BOA-CI</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>APKA Jacques</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>GONNE</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Marie-Madeleine</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>GONNE Marie-Madeleine</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0757381753</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Evaluation du dispositif de contrôle interne dans la gestion d'une station-service: cas de la station service Bêta de PETRO IVOIRE SA</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>PETRO IVOIRE SA</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>AHOGNISSO Angeline</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>KOUADIO</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Bini Eliel</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>KOUADIO Bini Eliel</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0788549653</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>La contribution des procédures d'audit légal dans la fiabilisation de l'information financière</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MLIN</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Melissa Laurenne</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>MLIN Melissa Laurenne</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0788155985</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Effet de l'absence de contrôle interne dans la gestion comptable et financière des offices notariaux: Cas de de l'étude de Maitre KONAN Attin Mathieu</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Simon</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>45386</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>OUATTARA</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Sienfoungo Marie-Louise</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OUATTARA Sienfoungo Marie-Louise</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0748</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Evaluation des risques dans une société de Gestion Immoilière: Une approche d'audit pour la prévention et la détection des risques de fraudes dans la société Beta</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Fofana César</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>45761</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>KOUADIO</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Jeanne Liliane Kousso</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>KOUADIO Jeanne Liliane Kousso</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0749089048</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Cartographie du processus d'octroi de crédit d'une Microfinance: Cas de CELPAID Finance</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>CELPAID Finance</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>TANOH</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Charles Philemon Donald</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>TANOH Charles Philemon Donald</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Audit des prélèvement sociaux sur les rémunérations des agents de l'entreprise Omega par un cabinet d'expertise comptable: Cas de prélèvement CMU</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>AHOGNISSO Angéline</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>AYEREBI</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Tanoa Olivia Sévérine Hermine</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>AYEREBI Tanoa Olivia Sévérine Hermine</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0778963064</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Education, adoption des nouvelles technologies et productivité agricole: cas de la Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>KOUAKOU Auguste</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>DEGALY</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Wilson Emilia Delsy</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DEGALY Wilson Emilia Delsy</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0502151776</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Audit des procédures de passation de commandes publiques exécuté au titre de la gestion budgetaire 2023: Cas de l'entité Alpha</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>FOFANA Cesar</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BADA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Achie Noura Carmelle</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BADA Achie Noura Carmelle</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>0779135993</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Problématique de financement bancaire pour le cycle d'exploitation des PME</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>KOUASSI Cyriaque</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>45397</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SADIE</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Yann Michel</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SADIE Yann Michel</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0102638915</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>L'influence d'une éducation financière sur l'amélioration de la bancarisation en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>DOMOA Danielle</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>45397</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BREDOU</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Assouema Stephanie</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BREDOU Assouema Stephanie</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>O709981418</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>La gestion des sinistres liés aux produits d'assurance en banque: cas du produit d'assurance YACONFORT de la SOCIETE GENERALE de Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>SOCIETE GENERALE</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>DOMOA Danielle</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>45397</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SORO</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Daouda Gnekognan</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SORO Daouda Gnekognan</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0747236343</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Stratégie marketing pour l'accroissement d'une banque: Cas de la BDU-CI</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>BDU-CI</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>KONAN Amoin Lucie</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>45397</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASSAMOI </t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Akoun Rosemonde Charlene</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ASSAMOI  Akoun Rosemonde Charlene</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0141219134</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>L'importance de l'évaluation des immobilisations corporelles dans la gestion efficace des établissements scolaires privés d'abidjan: cas de ALHPA</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>SANGARE Tchetien</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>45397</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>N'GUESSAN</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Timy Urielle Sephora</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Timy Urielle Sephora</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0787831715</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Evaluation du dispositif de contrôle interne dans les sociétés de gestion et d'intermédiation</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>N'DRI Yachine</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>AFOUMOU</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Ange Alex</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>AFOUMOU Ange Alex</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0556040441</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>L'impact de l'inétgration des nouvelles technologies sur le processus de compensation bancaire: cas de AFG BANK</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>AFG BANK</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>SANGARE Tchetien</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>BOUADOU-NIDA</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Sara Gbocho Eliel</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BOUADOU-NIDA Sara Gbocho Eliel</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0749778822</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Audit des immobilisations corporelles et la fiabilité de l'information financière: cas de la société LEAD PRODUCT</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>LEAD PRODUCT</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>OUATTARA Bassife</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>LOGBO</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Amakouba Tiffany</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>LOGBO Amakouba Tiffany</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>0777966985</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Audit des créances clients dans un établissement de restauration: cas du Restaurant Angola</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Restaurant Angola</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>BADINI Haoua</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>TOHOUA</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Dekassan Lionel</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>TOHOUA Dekassan Lionel</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0789868565</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>La contribution de l'audit externe à la gestion des risques fiscaux: Cas de l'entreprise Delta</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>BADINI Haoua</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SANOGO</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Mohamed Bantche</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>SANOGO Mohamed Bantche</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0710806273</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Elaboration d'un manuel de procédures comptables: cas de l'entreprise X</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>FOFANA Adon</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SETONDJI</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Magloire Gilchrist K.D</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>SETONDJI Magloire Gilchrist K.D</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0103547878</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Audit de projet d'une ONG financée par le fond Américain PEPFAR: Cas de médecins humanistes</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>AHOGNISSO Angeline</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ESMEL</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Amari Evrard Ulrich</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>ESMEL Amari Evrard Ulrich</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0152521053</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Evaluation du dispositif de contrôle interne dans la gestion d'une station-service: cas de la station service Bêta de PETRO IVOIRE SA</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>AKA Brou</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>KADJO</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Aimée Jocelyne Berthe</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>KADJO Aimée Jocelyne Berthe</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0788549653</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Facteurs explicatifs du Ralentissement dans le traitement de l'information entre agence locale et le siège de SANLAM ALLIANZ: cas de l'agence locale OBE-Live d'Attobant</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>SANLAM ALLIANZ</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>BEDA Clotaire</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>MOUNDIN</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Moumbagna Aboubakar Sidick</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>MOUNDIN Moumbagna Aboubakar Sidick</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0152240877</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Stratégie de conquête des clients par AFGBANK CI</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>AFGBANK</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>KONAN Amoin Lucie</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>45762</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>YABO</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ossondoh Martial</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>YABO Ossondoh Martial</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Analyse des risques opérationnels bancaires dans un processus des fusions acquisition: cas d'AFG BANK</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Banque et assurance</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>AFG BANK</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>N'GUESSAN Simon</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>45763</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>MIAKO</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Jean Yves Arnold</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>MIAKO Jean Yves Arnold</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0103926375</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Effet de la croissance économique sur les inégalités de revenus</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>ASSOUMOU Giscard</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>GNAMBA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Grâce Juvenal</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>GNAMBA Grâce Juvenal</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Investissements directs étrangers et croissance économique en Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>économie du développement</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>AKA Brou</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>45764</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SENY</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Mariam Leka</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SENY Mariam Leka</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0777918656</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Mise en place d'un système de pilotage de la performance dans le secteur des paiements: Cas de GIH-UEMOA</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Audit et contrôle</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>GIH-UEMOA</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>KONAN Lucie</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bd1.xlsx
+++ b/bd1.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\père kpoda\env\Pere_kpoda\Pere_kpoda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\père kpoda\env\Pere_kpoda\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Graphique3" sheetId="7" r:id="rId1"/>
-    <sheet name="Feuil3" sheetId="6" r:id="rId2"/>
+    <sheet name="Graphique1" sheetId="9" r:id="rId1"/>
+    <sheet name="Feuil1" sheetId="8" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="26" r:id="rId4"/>
+    <pivotCache cacheId="9" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="949">
   <si>
     <t>Date de dépôt</t>
   </si>
@@ -2878,7 +2878,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -2934,7 +2934,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -2968,7 +2968,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[bd1.xlsx]Feuil3!Tableau croisé dynamique15</c:name>
+    <c:name>[bd1.xlsx]Feuil1!Tableau croisé dynamique5</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -3072,7 +3072,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil3!$C$3</c:f>
+              <c:f>Feuil1!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3093,7 +3093,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>Feuil3!$A$4:$B$76</c:f>
+              <c:f>Feuil1!$A$4:$B$76</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="73"/>
                 <c:lvl>
@@ -3330,7 +3330,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Feuil3!$C$4:$C$76</c:f>
+              <c:f>Feuil1!$C$4:$C$76</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="73"/>
@@ -3338,7 +3338,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -3558,7 +3558,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0268-482F-9429-8D6FA6E565EF}"/>
+              <c16:uniqueId val="{00000000-5C28-49B1-8451-853D566848A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3571,11 +3571,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="923418623"/>
-        <c:axId val="923420703"/>
+        <c:axId val="534024799"/>
+        <c:axId val="534025215"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="923418623"/>
+        <c:axId val="534024799"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3618,7 +3618,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="923420703"/>
+        <c:crossAx val="534025215"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3626,7 +3626,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="923420703"/>
+        <c:axId val="534025215"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3677,7 +3677,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="923418623"/>
+        <c:crossAx val="534024799"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4317,7 +4317,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="45793.050437962964" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="186">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="HP" refreshedDate="45794.60682789352" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="186">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:M187" sheet="Sheet1"/>
   </cacheSource>
@@ -6242,7 +6242,7 @@
     <s v="Audit et contrôle"/>
     <s v="Audit et contrôle"/>
     <x v="0"/>
-    <x v="9"/>
+    <x v="0"/>
     <s v="SANGARE Tchétien"/>
     <m/>
     <m/>
@@ -7241,7 +7241,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tableau croisé dynamique15" cacheId="26" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tableau croisé dynamique5" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:C76" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="13">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -7989,7 +7989,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -12489,6 +12489,9 @@
       <c r="I121" t="s">
         <v>19</v>
       </c>
+      <c r="J121" t="s">
+        <v>20</v>
+      </c>
       <c r="K121" t="s">
         <v>600</v>
       </c>

--- a/bd1.xlsx
+++ b/bd1.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -2998,7 +2998,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7241,7 +7240,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tableau croisé dynamique5" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tableau croisé dynamique5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2">
   <location ref="A3:C76" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="13">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
